--- a/DbSchema.xlsx
+++ b/DbSchema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Language\Projects\AlanCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFA0FD4-50FE-4315-8A97-D084A4BFE05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F5F28A-4089-4FBF-8AE3-717113EBD46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserData" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
   <si>
     <t>UserId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t>nit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一筆訂單只會有一個賣家，如果買家一次買2個人的，會自動分2筆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from CartOfUser.Stock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buyer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -625,6 +637,9 @@
       <c r="E3" t="s">
         <v>22</v>
       </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -801,6 +816,9 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -912,6 +930,9 @@
       <c r="E5" t="s">
         <v>18</v>
       </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">

--- a/DbSchema.xlsx
+++ b/DbSchema.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Language\Projects\AlanCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F5F28A-4089-4FBF-8AE3-717113EBD46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9A79E9-C5CD-4844-97EC-19C973C4F91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UserData" sheetId="1" r:id="rId1"/>
-    <sheet name="CartOfUser" sheetId="2" r:id="rId2"/>
-    <sheet name="ProductData" sheetId="3" r:id="rId3"/>
-    <sheet name="OrderData" sheetId="4" r:id="rId4"/>
-    <sheet name="OrderItem" sheetId="5" r:id="rId5"/>
+    <sheet name="CartOfUser" sheetId="2" r:id="rId1"/>
+    <sheet name="ProductData" sheetId="3" r:id="rId2"/>
+    <sheet name="OrderData" sheetId="4" r:id="rId3"/>
+    <sheet name="OrderItem" sheetId="5" r:id="rId4"/>
+    <sheet name="UserData" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="46">
   <si>
     <t>UserId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,6 +187,30 @@
   </si>
   <si>
     <t>buyer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBuyerConfirmed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>買家審認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>賣家結單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsSellerClosed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -511,78 +535,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFE0C7-6A01-4715-A6B5-62F07C4A66DA}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="40.5703125" customWidth="1"/>
-  </cols>
   <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -592,11 +610,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFE0C7-6A01-4715-A6B5-62F07C4A66DA}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9509203D-8907-4AF0-A68B-830FF8AC5D9D}">
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>12</v>
       </c>
@@ -613,10 +636,13 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -624,40 +650,61 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" t="s">
-        <v>22</v>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -667,16 +714,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9509203D-8907-4AF0-A68B-830FF8AC5D9D}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104E18AD-0A57-40E5-9016-2E1DE913B9EE}">
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>12</v>
       </c>
@@ -693,10 +738,13 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -707,7 +755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -717,48 +765,72 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -768,14 +840,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104E18AD-0A57-40E5-9016-2E1DE913B9EE}">
-  <dimension ref="A1:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75EBB1E-E08C-426F-AF81-72B3B2B5DC5F}">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>12</v>
       </c>
@@ -792,10 +864,13 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -806,43 +881,40 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -851,9 +923,6 @@
       </c>
       <c r="F6" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -863,86 +932,81 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75EBB1E-E08C-426F-AF81-72B3B2B5DC5F}">
-  <dimension ref="A1:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:H7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
       <c r="E3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/DbSchema.xlsx
+++ b/DbSchema.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Language\Projects\AlanCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9A79E9-C5CD-4844-97EC-19C973C4F91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769C90C3-232C-48A4-925B-E44FA36E4ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CartOfUser" sheetId="2" r:id="rId1"/>
     <sheet name="ProductData" sheetId="3" r:id="rId2"/>
     <sheet name="OrderData" sheetId="4" r:id="rId3"/>
-    <sheet name="OrderItem" sheetId="5" r:id="rId4"/>
-    <sheet name="UserData" sheetId="1" r:id="rId5"/>
+    <sheet name="工作表1" sheetId="6" r:id="rId4"/>
+    <sheet name="OrderItem" sheetId="5" r:id="rId5"/>
+    <sheet name="UserData" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -840,6 +841,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463A0C92-E549-47A8-92FE-C2D547678E94}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75EBB1E-E08C-426F-AF81-72B3B2B5DC5F}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -931,7 +943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:H7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
